--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682944</v>
+        <v>121680348</v>
       </c>
       <c r="B2" t="n">
-        <v>57838</v>
+        <v>57376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587074</v>
+        <v>586941</v>
       </c>
       <c r="R2" t="n">
-        <v>6640685</v>
+        <v>6640592</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680696</v>
+        <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587150</v>
+        <v>587074</v>
       </c>
       <c r="R3" t="n">
-        <v>6640601</v>
+        <v>6640685</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680348</v>
+        <v>121680696</v>
       </c>
       <c r="B4" t="n">
-        <v>57376</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586941</v>
+        <v>587150</v>
       </c>
       <c r="R4" t="n">
-        <v>6640592</v>
+        <v>6640601</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R3" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680696</v>
+        <v>121682944</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587150</v>
+        <v>587074</v>
       </c>
       <c r="R4" t="n">
-        <v>6640601</v>
+        <v>6640685</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B2" t="n">
-        <v>57376</v>
+        <v>57838</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R2" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R3" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B4" t="n">
-        <v>57838</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R4" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680348</v>
+        <v>121680696</v>
       </c>
       <c r="B3" t="n">
-        <v>57376</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586941</v>
+        <v>587150</v>
       </c>
       <c r="R3" t="n">
-        <v>6640592</v>
+        <v>6640601</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R4" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680348</v>
+        <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57376</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586941</v>
+        <v>587150</v>
       </c>
       <c r="R2" t="n">
-        <v>6640592</v>
+        <v>6640601</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>57376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R4" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682944</v>
+        <v>121680348</v>
       </c>
       <c r="B3" t="n">
-        <v>57838</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587074</v>
+        <v>586941</v>
       </c>
       <c r="R3" t="n">
-        <v>6640685</v>
+        <v>6640592</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B4" t="n">
-        <v>57376</v>
+        <v>57846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R4" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680696</v>
+        <v>121682944</v>
       </c>
       <c r="B2" t="n">
-        <v>57381</v>
+        <v>57846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587150</v>
+        <v>587074</v>
       </c>
       <c r="R2" t="n">
-        <v>6640601</v>
+        <v>6640685</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B4" t="n">
-        <v>57846</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R4" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682944</v>
+        <v>121680348</v>
       </c>
       <c r="B2" t="n">
-        <v>57846</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587074</v>
+        <v>586941</v>
       </c>
       <c r="R2" t="n">
-        <v>6640685</v>
+        <v>6640592</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +800,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>57846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R3" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +932,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680348</v>
+        <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586941</v>
+        <v>587150</v>
       </c>
       <c r="R2" t="n">
-        <v>6640592</v>
+        <v>6640601</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,7 +803,7 @@
         <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57846</v>
+        <v>57850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B4" t="n">
-        <v>57381</v>
+        <v>57388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R4" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B2" t="n">
-        <v>57385</v>
+        <v>57391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R2" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B3" t="n">
-        <v>57850</v>
+        <v>57388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R3" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B4" t="n">
-        <v>57388</v>
+        <v>57854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R4" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680348</v>
+        <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57391</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586941</v>
+        <v>587150</v>
       </c>
       <c r="R2" t="n">
-        <v>6640592</v>
+        <v>6640601</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B3" t="n">
-        <v>57388</v>
+        <v>57393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R3" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121682944</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680696</v>
+        <v>121682944</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>57856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587150</v>
+        <v>587074</v>
       </c>
       <c r="R2" t="n">
-        <v>6640601</v>
+        <v>6640685</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B4" t="n">
-        <v>57856</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R4" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682944</v>
+        <v>121680348</v>
       </c>
       <c r="B2" t="n">
-        <v>57856</v>
+        <v>57393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587074</v>
+        <v>586941</v>
       </c>
       <c r="R2" t="n">
-        <v>6640685</v>
+        <v>6640592</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57393</v>
+        <v>57856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R3" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B2" t="n">
-        <v>57393</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R2" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682944</v>
+        <v>121680348</v>
       </c>
       <c r="B3" t="n">
-        <v>57856</v>
+        <v>57398</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587074</v>
+        <v>586941</v>
       </c>
       <c r="R3" t="n">
-        <v>6640685</v>
+        <v>6640592</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +928,7 @@
         <v>121680696</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R2" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121680348</v>
+        <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57398</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586941</v>
+        <v>587074</v>
       </c>
       <c r="R3" t="n">
-        <v>6640592</v>
+        <v>6640685</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:46</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680696</v>
+        <v>121680348</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587150</v>
+        <v>586941</v>
       </c>
       <c r="R4" t="n">
-        <v>6640601</v>
+        <v>6640592</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100049</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -818,11 +813,6 @@
       <c r="E3" t="n">
         <v>103018</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Ficedula hypoleuca</t>
@@ -942,11 +932,6 @@
       </c>
       <c r="E4" t="n">
         <v>102977</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121680696</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -798,7 +803,7 @@
         <v>121682944</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>57865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,6 +817,11 @@
       </c>
       <c r="E3" t="n">
         <v>103018</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -918,7 +928,7 @@
         <v>121680348</v>
       </c>
       <c r="B4" t="n">
-        <v>57398</v>
+        <v>57402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,6 +942,11 @@
       </c>
       <c r="E4" t="n">
         <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 17919-2020 artfynd.xlsx
+++ b/artfynd/A 17919-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680696</v>
+        <v>121682944</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587150</v>
+        <v>587074</v>
       </c>
       <c r="R2" t="n">
-        <v>6640601</v>
+        <v>6640685</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121682944</v>
+        <v>121680696</v>
       </c>
       <c r="B3" t="n">
-        <v>57865</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,21 +816,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587074</v>
+        <v>587150</v>
       </c>
       <c r="R3" t="n">
-        <v>6640685</v>
+        <v>6640601</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
